--- a/outputs/41978.xlsx
+++ b/outputs/41978.xlsx
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="17" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G2)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G2,$J$14:$J$185,"open")</f>
         <v>0</v>
       </c>
       <c r="J2" s="18" t="s">
@@ -1198,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G3)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G3,$J$14:$J$185,"open")</f>
         <v>0</v>
       </c>
       <c r="J3" s="26" t="s">
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G4)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G4,$J$14:$J$185,"open")</f>
         <v>0</v>
       </c>
       <c r="J4" s="30" t="s">
@@ -1254,7 +1254,7 @@
         <v>38</v>
       </c>
       <c r="I5" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G5)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G5,$J$14:$J$185,"open")</f>
         <v>2</v>
       </c>
       <c r="J5" s="33"/>
@@ -1280,7 +1280,7 @@
         <v>11</v>
       </c>
       <c r="I6" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G6)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G6,$J$14:$J$185,"open")</f>
         <v>0</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         <v>43</v>
       </c>
       <c r="I7" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G7)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G7,$J$14:$J$185,"open")</f>
         <v>0</v>
       </c>
       <c r="J7" s="38"/>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="I8" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G8)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G8,$J$14:$J$185,"open")</f>
         <v>1</v>
       </c>
       <c r="J8" s="38"/>
@@ -1341,7 +1341,7 @@
         <v>39</v>
       </c>
       <c r="I9" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G9)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G9,$J$14:$J$185,"open")</f>
         <v>26</v>
       </c>
       <c r="J9" s="38"/>
@@ -1361,7 +1361,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G10)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G10,$J$14:$J$185,"open")</f>
         <v>9</v>
       </c>
       <c r="J10" s="38"/>
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="25" t="n">
-        <f aca="false">SUMPRODUCT(($G$14:$G$185=G11)*(UPPER($J$14:$J$185)="OPEN"))</f>
+        <f aca="false">COUNTIFS($G$14:$G$185,G11,$J$14:$J$185,"open")</f>
         <v>2</v>
       </c>
     </row>

--- a/outputs/41978.xlsx
+++ b/outputs/41978.xlsx
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="17" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G2,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2013",J14:J185,"open")</f>
         <v>0</v>
       </c>
       <c r="J2" s="18" t="s">
@@ -1198,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G3,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2014",J14:J185,"open")</f>
         <v>0</v>
       </c>
       <c r="J3" s="26" t="s">
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G4,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2015",J14:J185,"open")</f>
         <v>0</v>
       </c>
       <c r="J4" s="30" t="s">
@@ -1254,7 +1254,7 @@
         <v>38</v>
       </c>
       <c r="I5" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G5,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2016",J14:J185,"open")</f>
         <v>2</v>
       </c>
       <c r="J5" s="33"/>
@@ -1280,7 +1280,7 @@
         <v>11</v>
       </c>
       <c r="I6" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G6,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2017",J14:J185,"open")</f>
         <v>0</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         <v>43</v>
       </c>
       <c r="I7" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G7,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2018",J14:J185,"open")</f>
         <v>0</v>
       </c>
       <c r="J7" s="38"/>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="I8" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G8,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2019",J14:J185,"open")</f>
         <v>1</v>
       </c>
       <c r="J8" s="38"/>
@@ -1341,7 +1341,7 @@
         <v>39</v>
       </c>
       <c r="I9" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G9,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2020",J14:J185,"open")</f>
         <v>26</v>
       </c>
       <c r="J9" s="38"/>
@@ -1361,7 +1361,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G10,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2021",J14:J185,"open")</f>
         <v>9</v>
       </c>
       <c r="J10" s="38"/>
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="25" t="n">
-        <f aca="false">COUNTIFS($G$14:$G$185,G11,$J$14:$J$185,"open")</f>
+        <f aca="false">COUNTIFS(G14:G185,"2022",J14:J185,"open")</f>
         <v>2</v>
       </c>
     </row>
